--- a/artfynd/A 59493-2024 artfynd.xlsx
+++ b/artfynd/A 59493-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128262334</v>
       </c>
       <c r="B2" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2024 artfynd.xlsx
+++ b/artfynd/A 59493-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128262334</v>
       </c>
       <c r="B2" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2024 artfynd.xlsx
+++ b/artfynd/A 59493-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128262334</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2024 artfynd.xlsx
+++ b/artfynd/A 59493-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128262334</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2024 artfynd.xlsx
+++ b/artfynd/A 59493-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128262334</v>
       </c>
       <c r="B2" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2024 artfynd.xlsx
+++ b/artfynd/A 59493-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128262334</v>
       </c>
       <c r="B2" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
